--- a/output/pdf_financials_xlsx/UCU.xlsx
+++ b/output/pdf_financials_xlsx/UCU.xlsx
@@ -1075,55 +1075,55 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.09876799999999999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.031387</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.010765</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.07960399999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.042884</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.016233</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.057029</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.005587</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.010152</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.007828</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.001002</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.019539</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.009253000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.003295</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.013955</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.006231</v>
       </c>
       <c r="S12" s="1" t="inlineStr">
         <is>
@@ -2086,55 +2086,55 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.979671</v>
+        <v>-4.078439</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.337731</v>
+        <v>-1.369118</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.347259</v>
+        <v>-3.358024</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.535153</v>
+        <v>-3.614757</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.682894</v>
+        <v>-5.725778</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.011274</v>
+        <v>-4.027507</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.927943</v>
+        <v>-3.984972</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-4.525003</v>
+        <v>-4.53059</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-5.39639</v>
+        <v>-5.406542</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-4.883342</v>
+        <v>-4.89117</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.76563</v>
+        <v>-4.766632</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-10.809972</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-5.526137</v>
+        <v>-5.545676</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-5.510747</v>
+        <v>-5.52</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-5.468915</v>
+        <v>-5.47221</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-7.605447</v>
+        <v>-7.619402</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-13.469998</v>
+        <v>-13.476229</v>
       </c>
       <c r="S27" s="1" t="inlineStr">
         <is>
@@ -2212,55 +2212,55 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.979671</v>
+        <v>-4.078439</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.337731</v>
+        <v>-1.369118</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.347259</v>
+        <v>-3.358024</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.535153</v>
+        <v>-3.614757</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.682894</v>
+        <v>-5.725778</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.011274</v>
+        <v>-4.027507</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.927943</v>
+        <v>-3.984972</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.525003</v>
+        <v>-4.53059</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.39639</v>
+        <v>-5.406542</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-4.883342</v>
+        <v>-4.89117</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.76563</v>
+        <v>-4.766632</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-10.809972</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.526137</v>
+        <v>-5.545676</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.510747</v>
+        <v>-5.52</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-5.468915</v>
+        <v>-5.47221</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-7.605447</v>
+        <v>-7.619402</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-13.469998</v>
+        <v>-13.476229</v>
       </c>
       <c r="S29" s="1" t="inlineStr">
         <is>
@@ -2539,58 +2539,58 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.04643</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.18383</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.18383</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.268265</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.30212</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.31177</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.328659</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.733673</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>3.1142</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.065664</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.461475</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.813492</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.008838</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>3.331164</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>2.261981</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.248382</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.627522</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>26.114089</v>
       </c>
     </row>
     <row r="35">
@@ -2661,58 +2661,58 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.0025</v>
+        <v>0.04893</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.015</v>
+        <v>0.19883</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.015</v>
+        <v>0.19883</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.276765</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.00375</v>
+        <v>0.30587</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.00075</v>
+        <v>1.31252</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.001</v>
+        <v>2.329659</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.00075</v>
+        <v>2.734423</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.001</v>
+        <v>3.1152</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.001</v>
+        <v>2.066664</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.0015</v>
+        <v>0.462975</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.001</v>
+        <v>2.814492</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.027833</v>
+        <v>1.036671</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.001</v>
+        <v>3.332164</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.0015</v>
+        <v>2.263481</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.248382</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.627522</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>26.114089</v>
       </c>
     </row>
     <row r="37">
@@ -3393,58 +3393,58 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.469221</v>
+        <v>1.422791</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.235901</v>
+        <v>2.052071</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.198914</v>
+        <v>2.015084</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7.845974</v>
+        <v>7.577709</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.279979</v>
+        <v>1.977859</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.487465</v>
+        <v>1.175695</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.844311</v>
+        <v>0.515652</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.275494</v>
+        <v>0.541821</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.399379</v>
+        <v>0.285179</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.24768</v>
+        <v>0.182016</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.694924</v>
+        <v>0.233449</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.041506</v>
+        <v>0.228014</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.225376</v>
+        <v>0.216538</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3.564511</v>
+        <v>0.233347</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.497549</v>
+        <v>0.235568</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.790821</v>
+        <v>0.542439</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.986737</v>
+        <v>0.359215</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>26.643728</v>
+        <v>0.529639</v>
       </c>
     </row>
     <row r="49">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -22342,7 +22342,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -23734,7 +23734,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
@@ -52034,7 +52034,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -56082,7 +56082,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -57696,7 +57696,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -62812,7 +62812,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E519" s="5" t="n">

--- a/output/pdf_financials_xlsx/UCU.xlsx
+++ b/output/pdf_financials_xlsx/UCU.xlsx
@@ -8015,7 +8015,7 @@
         <v>0</v>
       </c>
       <c r="R120" s="3" t="n">
-        <v>0</v>
+        <v>2.298541</v>
       </c>
       <c r="S120" s="3" t="n">
         <v>2.405816</v>
@@ -28310,7 +28310,11 @@
           <t>Proceeds from the issuance of common shares, net of issuance costs (note 13)</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
